--- a/testakten/hoai-leistungsphasen-kita-muehlenhof-lichtenrade-2026/07-lph6-lv-und-mengenrisiko.xlsx
+++ b/testakten/hoai-leistungsphasen-kita-muehlenhof-lichtenrade-2026/07-lph6-lv-und-mengenrisiko.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lose" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vergabe_Budgetdrift" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mengen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,30 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002F6F73"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F3F1"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,12 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,46 +414,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>LV und Mengenrisiko LPH 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>LV und Vergabe-Budgetdrift ausgewaehlter Lose (Betraege netto in EUR)</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Los</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Leistung</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Mengenstatus</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ansatz Kostenberechnung LPH 3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LV-Summe LPH 6</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Guenstigstes Angebot LPH 7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Risiko</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Notiz</t>
         </is>
@@ -493,17 +479,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>teilweise geprüft</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>mittel</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Baugrund offen</t>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1690000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1720000</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>hoch</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Baugrund/Gruendung Nord-Ost offen</t>
         </is>
       </c>
     </row>
@@ -520,17 +515,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LV grob</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>640000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>660000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>735000</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>hoch</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Brandschutzdetails fehlen</t>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Brandschutzdetail Befestigung fehlt</t>
         </is>
       </c>
     </row>
@@ -542,22 +546,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TGA Lüftung</t>
+          <t>TGA gesamt (Lueftung/Kueche/PV)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nicht abgestimmt</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1190000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1210000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1320000</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>hoch</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Küchenabluft/Schallschutz</t>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kuechenabluft kollidiert mit Unterzug</t>
         </is>
       </c>
     </row>
@@ -569,29 +582,75 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Außenanlagen</t>
+          <t>Aussenanlagen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mengen offen</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>500</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>510000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>515000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>545000</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>mittel</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Entwässerung und Spielgeräte</t>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Entwaesserung und Spielgeraete</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Summe ausgewaehlte Lose</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>3990000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4075000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4320000</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Drift Angebot ./. Ansatz</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>330000</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Mehrkosten der bepreisten Lose</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -602,42 +661,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>LV und Mengenrisiko LPH 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Mengengeruest und Planbezug</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Menge LV</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Einheit</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Planbezug</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Prüfung</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Pruefung</t>
         </is>
       </c>
     </row>
@@ -652,19 +709,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A-602 B</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Index C fehlt</t>
+          <t>A-602 Index B</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Index C fehlt, Menge unbestaetigt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lüftungskanal Küche</t>
+          <t>Lueftungskanal Kueche</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -672,19 +734,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TGA-L-214 A</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Konflikt Unterzug</t>
+          <t>TGA-L-214 Index A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Konflikt mit Unterzug T-301</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dachbegrünung extensiv</t>
+          <t>Dachbegruenung extensiv</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -692,19 +759,71 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A-Dach C</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Statik offen</t>
+          <t>A-Dach Index C</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Statik der Auflast offen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bodenplatte Gruendung</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>640</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>T-301 Index B</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Baugrundgutachten Nord-Ost offen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Entwaesserungsrinne Hof</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>95</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A-Frei Index B</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Anschlusshoehen nicht abgestimmt</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>